--- a/pastoral-projects/screen-time/downloads/Screen_Time_Tracker.xlsx
+++ b/pastoral-projects/screen-time/downloads/Screen_Time_Tracker.xlsx
@@ -34,7 +34,7 @@
     <t xml:space="preserve">Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Average daily screen time per week (hours and minutes)</t>
+    <t xml:space="preserve">Average daily screen time per week (hours, e.g. 3.5)</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
